--- a/data/trans_orig/IQ27A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ27A-Estudios-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Talla media, en centímetros, referida por progenitor/a</t>
+          <t>Talla media, en centímetros, declarada por progenitor/a (tasa de respuesta: 90,55%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>128,32; 138,67</t>
+          <t>128,9; 139,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>122,91; 134,95</t>
+          <t>123,47; 135,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>115,4; 129,09</t>
+          <t>116,24; 129,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>118,24; 143,18</t>
+          <t>118,17; 143,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>123,7; 134,89</t>
+          <t>123,66; 135,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>123,51; 136,66</t>
+          <t>123,13; 136,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>125,83; 137,12</t>
+          <t>126,11; 137,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>120,8; 134,84</t>
+          <t>121,67; 134,76</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>127,68; 135,38</t>
+          <t>127,72; 135,5</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>125,47; 133,88</t>
+          <t>125,53; 134,02</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>122,68; 132,07</t>
+          <t>123,61; 132,03</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>122,64; 136,61</t>
+          <t>123,0; 136,35</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>124,0; 129,03</t>
+          <t>124,4; 129,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>118,38; 123,69</t>
+          <t>118,53; 123,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>123,37; 128,06</t>
+          <t>123,19; 127,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>130,72; 138,72</t>
+          <t>130,65; 139,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>126,96; 131,7</t>
+          <t>126,72; 132,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>120,55; 125,76</t>
+          <t>120,23; 125,67</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>123,05; 128,01</t>
+          <t>122,99; 128,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>135,67; 141,06</t>
+          <t>135,48; 141,37</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>126,55; 129,78</t>
+          <t>126,4; 129,93</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>120,27; 124,2</t>
+          <t>120,32; 124,04</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>123,87; 127,18</t>
+          <t>123,87; 127,33</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>134,05; 138,83</t>
+          <t>134,19; 138,66</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>116,04; 123,92</t>
+          <t>116,21; 124,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>113,74; 121,9</t>
+          <t>113,95; 121,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>112,4; 121,15</t>
+          <t>112,24; 120,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>129,47; 136,94</t>
+          <t>128,74; 136,73</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>116,93; 126,49</t>
+          <t>116,42; 125,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>114,38; 122,73</t>
+          <t>114,68; 123,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>115,2; 123,34</t>
+          <t>114,68; 123,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>132,32; 139,42</t>
+          <t>132,34; 139,7</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>117,85; 123,86</t>
+          <t>118,04; 123,66</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>115,48; 121,21</t>
+          <t>115,53; 121,36</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>115,04; 120,99</t>
+          <t>115,08; 120,86</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>132,07; 136,99</t>
+          <t>131,86; 137,37</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>124,21; 128,03</t>
+          <t>124,21; 128,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>119,23; 123,39</t>
+          <t>119,47; 123,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>121,04; 125,13</t>
+          <t>121,09; 125,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>131,12; 137,02</t>
+          <t>131,08; 137,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>125,69; 129,42</t>
+          <t>125,39; 129,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>120,57; 124,97</t>
+          <t>120,81; 124,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>122,47; 126,53</t>
+          <t>122,44; 126,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>134,73; 139,46</t>
+          <t>134,57; 139,15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>125,5; 128,29</t>
+          <t>125,42; 128,28</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>120,62; 123,62</t>
+          <t>120,69; 123,63</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>122,35; 125,16</t>
+          <t>122,48; 125,23</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>133,63; 137,41</t>
+          <t>133,62; 137,38</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ27A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ27A-Estudios-trans_orig.xlsx
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>128,9; 139,08</t>
+          <t>129,0; 138,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>123,47; 135,25</t>
+          <t>123,77; 135,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>116,24; 129,07</t>
+          <t>115,45; 129,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>118,17; 143,31</t>
+          <t>117,54; 143,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>123,66; 135,39</t>
+          <t>123,6; 134,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>123,13; 136,37</t>
+          <t>123,1; 135,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>126,11; 137,55</t>
+          <t>125,72; 137,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>121,67; 134,76</t>
+          <t>120,72; 134,54</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>127,72; 135,5</t>
+          <t>127,62; 135,17</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>125,53; 134,02</t>
+          <t>125,32; 133,87</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>123,61; 132,03</t>
+          <t>123,01; 132,27</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>123,0; 136,35</t>
+          <t>122,92; 136,82</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>124,4; 129,36</t>
+          <t>124,08; 129,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>118,53; 123,68</t>
+          <t>118,34; 123,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>123,19; 127,75</t>
+          <t>123,21; 127,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>130,65; 139,21</t>
+          <t>130,61; 138,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>126,72; 132,04</t>
+          <t>126,75; 131,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>120,23; 125,67</t>
+          <t>120,4; 125,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>122,99; 128,12</t>
+          <t>123,02; 127,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>135,48; 141,37</t>
+          <t>135,44; 141,2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>126,4; 129,93</t>
+          <t>126,37; 129,95</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>120,32; 124,04</t>
+          <t>120,26; 123,96</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>123,87; 127,33</t>
+          <t>123,77; 127,18</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>134,19; 138,66</t>
+          <t>134,05; 138,65</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>116,21; 124,1</t>
+          <t>116,37; 124,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>113,95; 121,87</t>
+          <t>114,06; 122,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>112,24; 120,57</t>
+          <t>112,47; 120,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>128,74; 136,73</t>
+          <t>129,47; 136,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>116,42; 125,9</t>
+          <t>116,91; 125,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>114,68; 123,35</t>
+          <t>114,81; 123,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>114,68; 123,65</t>
+          <t>114,96; 123,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>132,34; 139,7</t>
+          <t>131,94; 139,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>118,04; 123,66</t>
+          <t>117,89; 124,11</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>115,53; 121,36</t>
+          <t>115,35; 121,2</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>115,08; 120,86</t>
+          <t>114,68; 120,56</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>131,86; 137,37</t>
+          <t>131,84; 137,06</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>124,21; 128,07</t>
+          <t>124,07; 128,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>119,47; 123,72</t>
+          <t>119,31; 123,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>121,09; 125,16</t>
+          <t>121,11; 124,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>131,08; 137,35</t>
+          <t>131,11; 137,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>125,39; 129,53</t>
+          <t>125,48; 129,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>120,81; 124,97</t>
+          <t>120,66; 125,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>122,44; 126,57</t>
+          <t>122,5; 126,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>134,57; 139,15</t>
+          <t>134,74; 139,18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>125,42; 128,28</t>
+          <t>125,32; 128,2</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>120,69; 123,63</t>
+          <t>120,7; 123,51</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>122,48; 125,23</t>
+          <t>122,25; 125,1</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>133,62; 137,38</t>
+          <t>133,64; 137,26</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ27A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ27A-Estudios-trans_orig.xlsx
@@ -532,7 +532,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,42 +648,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>129,47</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>129,76</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>131,82</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>129,15</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>133,71</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>129,47</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>122,92</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>134,15</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>129,47</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>129,76</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>131,82</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>127,97</t>
+          <t>138,3</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>130,84</t>
+          <t>133,2</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>129,0; 138,77</t>
+          <t>123,7; 134,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>123,77; 135,23</t>
+          <t>123,51; 136,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>115,45; 129,84</t>
+          <t>125,83; 137,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>117,54; 143,12</t>
+          <t>121,68; 136,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>123,6; 134,83</t>
+          <t>128,32; 138,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>123,1; 135,98</t>
+          <t>122,91; 134,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>125,72; 137,55</t>
+          <t>115,4; 129,09</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>120,72; 134,54</t>
+          <t>131,37; 144,38</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>127,62; 135,17</t>
+          <t>127,68; 135,38</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>125,32; 133,87</t>
+          <t>125,47; 133,88</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>123,01; 132,27</t>
+          <t>122,68; 132,07</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>122,92; 136,82</t>
+          <t>128,2; 138,31</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>129,34</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>123,2</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>125,49</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>139,17</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>126,82</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>121,18</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>125,51</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>133,61</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>129,34</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>123,2</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>125,49</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>138,27</t>
+          <t>133,5</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>136,1</t>
+          <t>136,51</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>124,08; 129,3</t>
+          <t>126,96; 131,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>118,34; 123,67</t>
+          <t>120,55; 125,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>123,21; 127,98</t>
+          <t>123,05; 128,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>130,61; 138,83</t>
+          <t>136,77; 141,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>126,75; 131,81</t>
+          <t>124,0; 129,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>120,4; 125,72</t>
+          <t>118,38; 123,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>123,02; 127,85</t>
+          <t>123,37; 128,06</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>135,44; 141,2</t>
+          <t>131,21; 135,75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>126,37; 129,95</t>
+          <t>126,55; 129,78</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>120,26; 123,96</t>
+          <t>120,27; 124,2</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>123,77; 127,18</t>
+          <t>123,87; 127,18</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>134,05; 138,65</t>
+          <t>134,85; 138,33</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>121,23</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>118,7</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>119,23</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>137,11</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>120,39</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>118,05</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>116,59</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>133,07</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>121,23</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>118,7</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>119,23</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>135,81</t>
+          <t>134,46</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>134,55</t>
+          <t>135,83</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>116,37; 124,45</t>
+          <t>116,93; 126,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>114,06; 122,32</t>
+          <t>114,38; 122,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>112,47; 120,71</t>
+          <t>115,2; 123,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>129,47; 136,7</t>
+          <t>133,58; 140,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>116,91; 125,81</t>
+          <t>116,04; 123,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>114,81; 123,17</t>
+          <t>113,74; 121,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>114,96; 123,81</t>
+          <t>112,4; 121,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>131,94; 139,28</t>
+          <t>131,02; 138,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>117,89; 124,11</t>
+          <t>117,85; 123,86</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>115,35; 121,2</t>
+          <t>115,48; 121,21</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>114,68; 120,56</t>
+          <t>115,04; 120,99</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>131,84; 137,06</t>
+          <t>133,31; 138,17</t>
         </is>
       </c>
     </row>
@@ -1068,42 +1068,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>127,6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>122,81</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>124,47</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>137,89</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>126,08</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>121,45</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>123,11</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>133,53</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>127,6</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>122,81</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>124,47</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>136,87</t>
+          <t>134,08</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>135,32</t>
+          <t>136,1</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>124,07; 128,06</t>
+          <t>125,69; 129,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>119,31; 123,53</t>
+          <t>120,57; 124,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>121,11; 124,97</t>
+          <t>122,47; 126,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>131,11; 137,73</t>
+          <t>135,81; 140,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>125,48; 129,75</t>
+          <t>124,21; 128,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>120,66; 125,13</t>
+          <t>119,23; 123,39</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>122,5; 126,43</t>
+          <t>121,04; 125,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>134,74; 139,18</t>
+          <t>132,17; 135,85</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>125,32; 128,2</t>
+          <t>125,5; 128,29</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>120,7; 123,51</t>
+          <t>120,62; 123,62</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>122,25; 125,1</t>
+          <t>122,35; 125,16</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>133,64; 137,26</t>
+          <t>134,61; 137,5</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ27A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ27A-Estudios-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -526,7 +531,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Talla media, en centímetros, declarada por progenitor/a (tasa de respuesta: 90,55%)</t>
+          <t>Talla media, en centímetros, declarada por madres/padres (tasa de respuesta: 90,55%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -646,419 +651,271 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>129,47</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>129,76</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>131,82</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>129,15</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>133,71</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>129,47</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>122,92</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>138,3</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>131,69</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>129,61</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>127,55</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>133,2</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>129.4676648671107</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>129.7552484733604</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>131.819761316766</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>129.1474981277395</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>133.7112656434518</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>129.4706738731104</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>122.9160155483614</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>138.2997519539171</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>131.6909701381508</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>129.6059314055131</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>127.5548983423114</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>133.2034486739512</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>123,7; 134,89</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>123,51; 136,66</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>125,83; 137,12</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>121,68; 136,05</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>128,32; 138,67</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>122,91; 134,95</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>115,4; 129,09</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>131,37; 144,38</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>127,68; 135,38</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>125,47; 133,88</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>122,68; 132,07</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>128,2; 138,31</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>123.6991170026948</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>123.5087790737647</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>125.8286087306015</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>121.6761889626432</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>128.3174008765679</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>122.9082756640884</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>115.3984995213904</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>131.3681549366854</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>127.6765923811728</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>125.4679088083441</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>122.6814706622763</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>128.201420958789</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>134.8878886138153</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>136.6581810565312</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>137.1213161432684</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>136.0485767977169</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>138.6667762734467</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>134.945355923198</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>129.0850405307825</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>144.3764674666061</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>135.3832698548349</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>133.8805559673243</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>132.0735545360967</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>138.3148576311795</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>129,34</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>123,2</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>125,49</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>139,17</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>126,82</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>121,18</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>125,51</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>133,5</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>128,17</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>122,23</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>125,5</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>136,51</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>126,96; 131,7</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>120,55; 125,76</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>123,05; 128,01</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>136,77; 141,71</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>124,0; 129,03</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>118,38; 123,69</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>123,37; 128,06</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>131,21; 135,75</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>126,55; 129,78</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>120,27; 124,2</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>123,87; 127,18</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>134,85; 138,33</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>129.3406270198419</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>123.2006782808241</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>125.4877361815749</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>139.1696449878694</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>126.818759407493</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>121.1813655298985</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>125.5116045697421</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>133.4980326255676</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>128.1745284996158</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>122.2287858575405</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>125.4993990325192</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>136.5139671577139</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>121,23</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>118,7</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>119,23</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>137,11</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>120,39</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>118,05</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>116,59</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>134,46</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>120,79</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>118,38</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>117,96</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>135,83</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>126.9635258663029</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>120.5483915170269</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>123.0500083500252</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>136.7712475503196</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>124.0041787850327</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>118.3819833222826</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>123.3706996025109</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>131.206990831924</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>126.5477152993989</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>120.2685670370272</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>123.8710453800077</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>134.848305899502</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>116,93; 126,49</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>114,38; 122,73</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>115,2; 123,34</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>133,58; 140,46</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>116,04; 123,92</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>113,74; 121,9</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>112,4; 121,15</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>131,02; 138,2</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>117,85; 123,86</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>115,48; 121,21</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>115,04; 120,99</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>133,31; 138,17</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>131.7026344857964</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>125.76353682137</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>128.0141561885387</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>141.707377641685</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>129.0279253950742</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>123.693055348932</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>128.0559490298953</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>135.7458148760315</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>129.7834940024503</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>124.2033789166176</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>127.1821620238645</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>138.3300767476173</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1066,137 +923,269 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>127,6</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>122,81</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>124,47</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>137,89</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>126,08</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>121,45</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>123,11</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>134,08</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>126,86</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>122,15</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>123,81</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>136,1</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>121.2300389728095</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>118.6979005206798</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>119.2313539696471</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>137.1072544414973</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>120.393213371741</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>118.0513740185792</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>116.5852167425892</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>134.4640262054148</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>120.787593375016</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>118.3838342768174</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>117.9555441913684</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>135.8264453315435</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>125,69; 129,42</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>120,57; 124,97</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>122,47; 126,53</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>135,81; 140,04</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>124,21; 128,03</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>119,23; 123,39</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>121,04; 125,13</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>132,17; 135,85</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>125,5; 128,29</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>120,62; 123,62</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>122,35; 125,16</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>134,61; 137,5</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>116.9277524031436</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>114.3774274177692</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>115.1988895963279</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>133.5789913613683</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>116.0351289056084</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>113.7396195028294</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>112.4016313725926</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>131.0173585111594</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>117.8455555458985</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>115.4843544595801</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>115.0418302767035</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>133.3141739589639</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>126.4865485995589</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>122.7304465180403</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>123.3378947999332</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>140.4630163722123</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>123.921950054722</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>121.9028526071824</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>121.1483467172978</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>138.1957226913114</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>123.8635008133829</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>121.2056274946572</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>120.9881137094243</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>138.1681668793858</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>127.6017142499947</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>122.8060855486041</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>124.4699673129261</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>137.8890378198919</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>126.0817349585735</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>121.451920198091</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>123.1076750004209</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>134.0800544804829</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>126.8636054164643</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>122.146107666909</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>123.8076008298541</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>136.097912016179</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>125.692400831572</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>120.5735197268786</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>122.4716574692994</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>135.8101720034165</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>124.2082189124435</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>119.2276281825091</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>121.0442523413011</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>132.1681323960397</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>125.504495408449</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>120.6177732054363</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>122.3508589096817</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>134.613339420936</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>129.4201798362878</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>124.967872937956</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>126.5275194843106</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>140.0382938452524</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>128.0270864039212</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>123.3851391296335</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>125.1316997948789</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>135.84707567838</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>128.2946685045747</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>123.6205522900917</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>125.1572965178322</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>137.4981892296706</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1204,14 +1193,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
